--- a/tame_output/ON/bt/strategyON_20240401.xlsx
+++ b/tame_output/ON/bt/strategyON_20240401.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>42.0%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-68.9%</t>
+          <t>-69.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>110.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.7%</t>
+          <t>125.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.0%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,27 +992,27 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.9%</t>
+          <t>-47.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-62.8%</t>
+          <t>-64.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>498.9%</t>
+          <t>503.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-419.2%</t>
+          <t>-421.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-219.2%</t>
+          <t>-223.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-36.5%</t>
+          <t>-37.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-79.4%</t>
+          <t>-72.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-171.2%</t>
+          <t>-172.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.5%</t>
+          <t>-25.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-283.3%</t>
+          <t>-300.2%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.3%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-19.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-148.0%</t>
+          <t>-154.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-211.7%</t>
+          <t>-228.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-170.4%</t>
+          <t>-180.5%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.8%</t>
+          <t>-28.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-130.6%</t>
+          <t>-140.7%</t>
         </is>
       </c>
     </row>
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213499</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.587793653476741</v>
+        <v>-1.757330812233671</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.494868970782638</v>
+        <v>2.427054107279866</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.4557372966734629</v>
+        <v>0.2862001379165331</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.40378523449116</v>
+        <v>3.302062939237002</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416048</v>
+        <v>3.231167537416049</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.58445690696777</v>
+        <v>-1.7539940657247</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.504302419794795</v>
+        <v>2.436487556292023</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.4584293290924942</v>
+        <v>0.2888921703355645</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.413499204351147</v>
+        <v>3.311776909096989</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382331</v>
+        <v>3.235981977382332</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-1.951167958634316</v>
+        <v>-2.120705117391245</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.358724391171909</v>
+        <v>2.290909527669137</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.09171827742594862</v>
+        <v>-0.07781888133098114</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.194578965394952</v>
+        <v>3.092856670140794</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495502</v>
+        <v>3.278199702495503</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.336348349564388</v>
+        <v>-2.505885508321318</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.203194773612744</v>
+        <v>2.135379910109971</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.09171827742594862</v>
+        <v>-0.07781888133098114</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.193121504207815</v>
+        <v>3.091399208953657</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347059</v>
+        <v>3.29913614634706</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.680031122791051</v>
+        <v>-2.849568281547981</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.067490787776695</v>
+        <v>1.999675924273922</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.01618777460126958</v>
+        <v>-0.1857249333581993</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.130146996446101</v>
+        <v>3.028424701191943</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.037681473029399</v>
+        <v>-3.207218631786329</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.920536706337613</v>
+        <v>1.852721842834841</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.3738381248396177</v>
+        <v>-0.5433752835965475</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.911662844959349</v>
+        <v>2.809940549705192</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178248</v>
+        <v>3.315884374178249</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.044342413251547</v>
+        <v>-3.213879572008477</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.919645256949013</v>
+        <v>1.851830393446241</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.3738381248396177</v>
+        <v>-0.5433752835965475</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.913435771659609</v>
+        <v>2.811713476405451</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.476148206401334</v>
+        <v>-3.645685365158264</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.733255827156503</v>
+        <v>1.665440963653731</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.5102556212808846</v>
+        <v>-0.6797927800378145</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.817918161262253</v>
+        <v>2.716195866008095</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310986</v>
+        <v>3.284619513310987</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.802580735269078</v>
+        <v>-3.972117894026008</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.590967590611496</v>
+        <v>1.523152727108724</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.5927238717880328</v>
+        <v>-0.7622610305449626</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.756721985960055</v>
+        <v>2.654999690705897</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.804144886379381</v>
+        <v>-3.973682045136311</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.58892252182334</v>
+        <v>1.521107658320568</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.5927238717880328</v>
+        <v>-0.7622610305449626</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.75530257761602</v>
+        <v>2.653580282361863</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309428</v>
+        <v>3.311086391309429</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.167771131279694</v>
+        <v>-4.337308290036624</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.449959584097456</v>
+        <v>1.382144720594684</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.6909455086551586</v>
+        <v>-0.8604826674120885</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.702857155729986</v>
+        <v>2.601134860475828</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970909</v>
+        <v>3.30471571697091</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.165344066750976</v>
+        <v>-4.334881225507906</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.450184924914775</v>
+        <v>1.382370061412003</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.6912782904623102</v>
+        <v>-0.8608154492192401</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.701912001651527</v>
+        <v>2.600189706397369</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330526</v>
+        <v>3.300815818330527</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.573932843931654</v>
+        <v>-4.743470002688584</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.285510958057263</v>
+        <v>1.217696094554491</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.099867067642989</v>
+        <v>-1.269404226399919</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.455520279357879</v>
+        <v>2.353797984103721</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191741</v>
+        <v>3.302618194191742</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-4.986915328072748</v>
+        <v>-5.156452486829678</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.115503396872286</v>
+        <v>1.047688533369514</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.099867067642989</v>
+        <v>-1.269404226399919</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.45070571182934</v>
+        <v>2.348983416575182</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108643</v>
+        <v>3.305023265108644</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.403307202359746</v>
+        <v>-5.572844361116675</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.9469406977663639</v>
+        <v>0.8791258342635921</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.099867067642989</v>
+        <v>-1.269404226399919</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.448699762438217</v>
+        <v>2.346977467184059</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097825</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.77998421288959</v>
+        <v>-5.94952137164652</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.8065285842231051</v>
+        <v>0.7387137207203334</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.099867067642989</v>
+        <v>-1.269404226399919</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.458958453106896</v>
+        <v>2.357236157852738</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094121</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.793699077214701</v>
+        <v>-5.963236235971631</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.7971422036387561</v>
+        <v>0.7293273401359843</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.099867067642989</v>
+        <v>-1.269404226399919</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.455058018252591</v>
+        <v>2.353335722998433</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.40596051119929</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.106523876459681</v>
+        <v>-6.27606103521661</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.6704172039957652</v>
+        <v>0.6026023404929934</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.099867067642989</v>
+        <v>-1.269404226399919</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.453462938307592</v>
+        <v>2.351740643053434</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969599</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.111336914925018</v>
+        <v>-6.280874073681948</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.6722709645388383</v>
+        <v>0.6044561010360665</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.101413702345774</v>
+        <v>-1.270950861102704</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.456313933415128</v>
+        <v>2.354591638160971</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.419979433923092</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.544686023035254</v>
+        <v>-6.714223181792184</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.4949050167603408</v>
+        <v>0.427090153257569</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.101413702345774</v>
+        <v>-1.270950861102704</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.452287628880725</v>
+        <v>2.350565333626568</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297754</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-6.927687411777885</v>
+        <v>-7.097224570534815</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.3416023599417044</v>
+        <v>0.2737874964389326</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.101413702345774</v>
+        <v>-1.270950861102704</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.452185527559141</v>
+        <v>2.350463232304984</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.302672737949162</v>
+        <v>-7.472209896706092</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.1941797454446235</v>
+        <v>0.1263648819418517</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.476399028517052</v>
+        <v>-1.645936187273982</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.229765847827805</v>
+        <v>2.128043552573647</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.662203060453164</v>
+        <v>-7.831740219210094</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.0557179197410731</v>
+        <v>-0.01209694376169868</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.476399028517052</v>
+        <v>-1.645936187273982</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.235116151125855</v>
+        <v>2.133393855871697</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341317</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.988603089118177</v>
+        <v>-8.158140247875107</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.06692607176775445</v>
+        <v>-0.1347409352705262</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.802799057182065</v>
+        <v>-1.972336215938995</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.047192153884025</v>
+        <v>1.945469858629867</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776681</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-7.982126942324618</v>
+        <v>-8.151664101081547</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.06129386242856194</v>
+        <v>-0.1291087259313337</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.796322910388505</v>
+        <v>-1.965860069145435</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.05411959258193</v>
+        <v>1.952397297327772</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407492</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-7.978436017368206</v>
+        <v>-8.147973176125136</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.0598174924459971</v>
+        <v>-0.1276323559487693</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.796322910388505</v>
+        <v>-1.965860069145435</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.05411959258193</v>
+        <v>1.952397297327772</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611695</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.182694192698069</v>
+        <v>-8.352231351455</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1360075654593</v>
+        <v>-0.2038224289620727</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.923961855002494</v>
+        <v>-2.093499013759424</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.983049422932178</v>
+        <v>1.881327127678021</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.343333219186434</v>
+        <v>-8.512870377943365</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.19578062157021</v>
+        <v>-0.2635954850729827</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.03869532800489</v>
+        <v>-2.208232486761819</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.918691893615177</v>
+        <v>1.816969598361019</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910627</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.269863387518985</v>
+        <v>-8.439400546275916</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1510209874098094</v>
+        <v>-0.2188358509125816</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.965225496337441</v>
+        <v>-2.134762655094371</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.978145494109068</v>
+        <v>1.87642319885491</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.444987804905528</v>
+        <v>-8.614524963662459</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2065155336169098</v>
+        <v>-0.2743303971196824</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.140349913723985</v>
+        <v>-2.309887072480915</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.887626064424658</v>
+        <v>1.7859037691705</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.679439898920018</v>
+        <v>-8.848977057676949</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3075155361243018</v>
+        <v>-0.375330399627074</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.140349913723985</v>
+        <v>-2.309887072480915</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.880406899523062</v>
+        <v>1.778684604268904</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.967243743457256</v>
+        <v>-9.136780902214188</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4293092647131735</v>
+        <v>-0.4971241282159458</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.428153758261223</v>
+        <v>-2.597690917018153</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.701052402026743</v>
+        <v>1.599330106772585</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.197068190621081</v>
+        <v>-9.366605349378013</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.520123253740147</v>
+        <v>-0.5879381172429197</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.590801295331384</v>
+        <v>-2.760338454088314</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.604579669623203</v>
+        <v>1.502857374369045</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.429097110357343</v>
+        <v>-9.598634269114275</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6102410930055373</v>
+        <v>-0.6780559565083095</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.652813992519807</v>
+        <v>-2.822351151276737</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.570065779939264</v>
+        <v>1.468343484685106</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.37708159638853</v>
+        <v>-9.546618755145461</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5854445517316109</v>
+        <v>-0.6532594152343836</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.652813992519807</v>
+        <v>-2.822351151276737</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.574056115625664</v>
+        <v>1.472333820371507</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.51875343811265</v>
+        <v>-9.688290596869582</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6435885153200007</v>
+        <v>-0.7114033788227734</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.652813992519807</v>
+        <v>-2.822351151276737</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.572580888726923</v>
+        <v>1.470858593472765</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.617660178571926</v>
+        <v>-9.787197337328857</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6680978013388388</v>
+        <v>-0.7359126648416114</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.751720732979082</v>
+        <v>-2.921257891736012</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.52829025461623</v>
+        <v>1.426567959362072</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.418508071334827</v>
+        <v>-9.588045230091758</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.601488092090682</v>
+        <v>-0.6693029555934547</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.586398207029269</v>
+        <v>-2.755935365786199</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.614432636539435</v>
+        <v>1.512710341285277</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.192662918615415</v>
+        <v>-9.362200077372346</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.5015709579667087</v>
+        <v>-0.5693858214694814</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.544471531442105</v>
+        <v>-2.714008690199035</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.649167714927942</v>
+        <v>1.547445419673784</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.90638810629272</v>
+        <v>-9.075925265049651</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3859218884815721</v>
+        <v>-0.4537367519843443</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.544471531442105</v>
+        <v>-2.714008690199035</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.650306859484001</v>
+        <v>1.548584564229843</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.679592279219387</v>
+        <v>-8.849129437976318</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.2925697834901309</v>
+        <v>-0.3603846469929035</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.476357586820561</v>
+        <v>-2.645894745577491</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.693809000419035</v>
+        <v>1.592086705164877</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081569</v>
+        <v>3.76894809908157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.395683548290638</v>
+        <v>-8.565220707047569</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.1732725868799947</v>
+        <v>-0.2410874503827674</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.476357586820561</v>
+        <v>-2.645894745577491</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.699542704657672</v>
+        <v>1.597820409403513</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425329</v>
+        <v>3.72857435442533</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.148696298097686</v>
+        <v>-8.318233456854617</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.08421494919667927</v>
+        <v>-0.1520298126994519</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.229370336627609</v>
+        <v>-2.398907495384539</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.837997792379578</v>
+        <v>1.736275497125419</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702414</v>
+        <v>3.747699084702415</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-7.884859430893617</v>
+        <v>-8.054396589650548</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.01143631637204079</v>
+        <v>-0.05637854713073143</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.229370336627609</v>
+        <v>-2.398907495384539</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.82811431106667</v>
+        <v>1.726392015812512</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906229</v>
+        <v>3.76631350390623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-7.617617630025221</v>
+        <v>-7.787154788782151</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.1164984762200256</v>
+        <v>0.04868361271725341</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.229370336627609</v>
+        <v>-2.398907495384539</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.826279750567296</v>
+        <v>1.724557455313138</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.78468094578195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-7.341808466624737</v>
+        <v>-7.511345625381667</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.2265218266067586</v>
+        <v>0.1587069631039864</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.140351028348875</v>
+        <v>-2.309888187105805</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.879391020561076</v>
+        <v>1.777668725306917</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567246</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-7.072740878857757</v>
+        <v>-7.242278037614687</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.3348173678590438</v>
+        <v>0.2670025043562716</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.871283440581896</v>
+        <v>-2.040820599338826</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.041500079366757</v>
+        <v>1.939777784112598</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487773</v>
+        <v>3.789307536487775</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-6.808680940534961</v>
+        <v>-6.978218099291891</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.42718102702641</v>
+        <v>0.3593661635236378</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.6072235022591</v>
+        <v>-1.77676066101603</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.186675726198682</v>
+        <v>2.084953430944524</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309729</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-6.101601317030123</v>
+        <v>-6.271138475787053</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.7072258427680445</v>
+        <v>0.6394109792652722</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.6072235022591</v>
+        <v>-1.77676066101603</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.183888692538381</v>
+        <v>2.082166397284223</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858729</v>
+        <v>3.839370871858731</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-5.851960287044171</v>
+        <v>-6.021497445801101</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.8074258786502666</v>
+        <v>0.7396110151474944</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.357582472273148</v>
+        <v>-1.527119631030078</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.334016934417794</v>
+        <v>2.232294639163636</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-5.597418387703096</v>
+        <v>-5.766955546460025</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.9086094596074537</v>
+        <v>0.8407945961046819</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.103040572932072</v>
+        <v>-1.272577731689003</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.486108895243196</v>
+        <v>2.384386599989038</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761806</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-5.363937165473497</v>
+        <v>-5.533474324230427</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.009926377337146</v>
+        <v>0.9421115138343739</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8695593507024739</v>
+        <v>-1.039096509459404</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.634122057418808</v>
+        <v>2.532399762164649</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-5.184228635329625</v>
+        <v>-5.353765794086554</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.078917579081736</v>
+        <v>1.011102715578964</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.8123878465397778</v>
+        <v>-0.9819250052967081</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.665532749603466</v>
+        <v>2.563810454349308</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-5.051953161698738</v>
+        <v>-5.221490320455668</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.127195255281117</v>
+        <v>1.059380391778345</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6801123729088911</v>
+        <v>-0.8496495316658215</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.740265520529025</v>
+        <v>2.638543225274867</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-4.861353487025585</v>
+        <v>-5.030890645782515</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.206250185838015</v>
+        <v>1.138435322335243</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4895126982357383</v>
+        <v>-0.6590498569926686</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.857440386020554</v>
+        <v>2.755718090766395</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430986</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-4.612353688342004</v>
+        <v>-4.781890847098934</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.318756446535106</v>
+        <v>1.250941583032334</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.4895126982357383</v>
+        <v>-0.6590498569926686</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.870346727244212</v>
+        <v>2.768624431990054</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-4.717943678115109</v>
+        <v>-4.887480836872038</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.148544521026645</v>
+        <v>1.080729657523874</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.5951026880088426</v>
+        <v>-0.7646398467657729</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.679016803781131</v>
+        <v>2.577294508526973</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457904</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-4.736678580233706</v>
+        <v>-4.906215738990635</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.189594902056293</v>
+        <v>1.121780038553521</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.5951026880088426</v>
+        <v>-0.7646398467657729</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.727561145658217</v>
+        <v>2.625838850404059</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-4.459940405562893</v>
+        <v>-4.629477564319822</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.303669183910613</v>
+        <v>1.235854320407841</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.4132860268989168</v>
+        <v>-0.5828231856558471</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.840030154310167</v>
+        <v>2.738307859056009</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-4.333047999127823</v>
+        <v>-4.502585157884752</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.345712160231163</v>
+        <v>1.277897296728391</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2863936204638469</v>
+        <v>-0.4559307792207772</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.907451611917731</v>
+        <v>2.805729316663573</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568105</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-4.145460491217897</v>
+        <v>-4.314997649974826</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.41378655130004</v>
+        <v>1.345971687797268</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2863936204638469</v>
+        <v>-0.4559307792207772</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.900490999822638</v>
+        <v>2.79876870456848</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-3.903312097764038</v>
+        <v>-4.072849256520968</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.525108263062726</v>
+        <v>1.457293399559955</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2863936204638469</v>
+        <v>-0.4559307792207772</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.914953354203781</v>
+        <v>2.813231058949623</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192815</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-3.84008272599569</v>
+        <v>-4.009619884752619</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.544932132229261</v>
+        <v>1.477117268726489</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2863936204638469</v>
+        <v>-0.4559307792207772</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.909485474662976</v>
+        <v>2.807763179408818</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-3.653595033618684</v>
+        <v>-3.823132192375613</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.61702530319064</v>
+        <v>1.549210439687868</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.09990592808684062</v>
+        <v>-0.2694430868437709</v>
       </c>
       <c r="G1915" t="n">
-        <v>3.018876184099757</v>
+        <v>2.917153888845599</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-3.632445834715241</v>
+        <v>-3.80198299347217</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.633185960989343</v>
+        <v>1.565371097486571</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.07875672918339727</v>
+        <v>-0.2482938879403276</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.039266681679148</v>
+        <v>2.93754438642499</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788093</v>
+        <v>3.748324832788095</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-3.388680392731796</v>
+        <v>-3.558217551488726</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.726472846129771</v>
+        <v>1.658657982627</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.07875672918339727</v>
+        <v>-0.2482938879403276</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.035047390026199</v>
+        <v>2.933325094772041</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527524</v>
+        <v>3.824307657527526</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-3.124652325538536</v>
+        <v>-3.294189484295466</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.834208386927092</v>
+        <v>1.76639352342432</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.1231086696325563</v>
+        <v>-0.04642848912437403</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.158290943235787</v>
+        <v>3.056568647981629</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749183</v>
+        <v>3.826351398749185</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-2.874801931589462</v>
+        <v>-3.044339090346391</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.926890619490424</v>
+        <v>1.859075755987652</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.1231086696325563</v>
+        <v>-0.04642848912437403</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.151033018219489</v>
+        <v>3.049310722965331</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.39228309451242</v>
+        <v>3.700692971422914</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-2.576295147566221</v>
+        <v>-2.602684122933772</v>
       </c>
       <c r="E1920" t="n">
-        <v>2.049892456620369</v>
+        <v>2.039336866473348</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.1231086696325563</v>
+        <v>-0.04642848912437403</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.154632141740138</v>
+        <v>3.05290984648598</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240401.xlsx
+++ b/tame_output/ON/bt/strategyON_20240401.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-69.9%</t>
+          <t>-70.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.8%</t>
+          <t>109.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.1%</t>
+          <t>93.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-64.0%</t>
+          <t>-64.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>503.4%</t>
+          <t>503.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-421.8%</t>
+          <t>-435.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-72.1%</t>
+          <t>-71.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-172.3%</t>
+          <t>-177.8%</t>
         </is>
       </c>
     </row>
@@ -45711,10 +45711,10 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-2.602684122933772</v>
+        <v>-2.740771601342413</v>
       </c>
       <c r="E1920" t="n">
-        <v>2.039336866473348</v>
+        <v>1.984101875109892</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.04642848912437403</v>

--- a/tame_output/ON/bt/strategyON_20240401.xlsx
+++ b/tame_output/ON/bt/strategyON_20240401.xlsx
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006538</v>
+        <v>3.305849539006539</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116218</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76894809908157</v>
+        <v>3.768948099081569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.72857435442533</v>
+        <v>3.728574354425329</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702415</v>
+        <v>3.747699084702414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631350390623</v>
+        <v>3.766313503906229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468094578195</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567246</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487775</v>
+        <v>3.789307536487773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309729</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858731</v>
+        <v>3.839370871858729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096477</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761806</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.753878996430986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457904</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192815</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.748324832788093</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527526</v>
+        <v>3.824307657527524</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749185</v>
+        <v>3.826351398749183</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.700692971422914</v>
+        <v>3.700692971422912</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>

--- a/tame_output/ON/bt/strategyON_20240401.xlsx
+++ b/tame_output/ON/bt/strategyON_20240401.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -671,12 +671,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>42.1%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,21 +801,21 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-9.4%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-64.9%</t>
+          <t>-65.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>503.0%</t>
+          <t>498.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-71.7%</t>
+          <t>-67.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-154.4%</t>
+          <t>-161.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.8%</t>
+          <t>-26.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-14.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-140.7%</t>
+          <t>-144.4%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1920"/>
+  <dimension ref="A1:G1921"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.700692971422912</v>
+        <v>3.835954411481496</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
@@ -45721,6 +45721,29 @@
       </c>
       <c r="G1920" t="n">
         <v>3.05290984648598</v>
+      </c>
+    </row>
+    <row r="1921">
+      <c r="A1921" s="2" t="n">
+        <v>45383</v>
+      </c>
+      <c r="B1921" t="n">
+        <v>3.701979533878345</v>
+      </c>
+      <c r="C1921" t="n">
+        <v>3.022725832109491</v>
+      </c>
+      <c r="D1921" t="n">
+        <v>-2.740771601342413</v>
+      </c>
+      <c r="E1921" t="n">
+        <v>1.984101875109892</v>
+      </c>
+      <c r="F1921" t="n">
+        <v>-0.04642848912437403</v>
+      </c>
+      <c r="G1921" t="n">
+        <v>3.015789629095859</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240401.xlsx
+++ b/tame_output/ON/bt/strategyON_20240401.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>12.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,12 +819,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-30.5%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,37 +839,37 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-34.0%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-70.5%</t>
+          <t>-70.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.9%</t>
+          <t>108.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.9%</t>
+          <t>123.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.1%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.6%</t>
+          <t>-46.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-65.4%</t>
+          <t>-66.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>498.8%</t>
+          <t>494.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-435.6%</t>
+          <t>-452.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-223.9%</t>
+          <t>-219.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.0%</t>
+          <t>-36.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-67.7%</t>
+          <t>-85.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-177.8%</t>
+          <t>-184.6%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.7%</t>
+          <t>-22.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-300.2%</t>
+          <t>-283.3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-32.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-19.1%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-161.2%</t>
+          <t>-155.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-228.6%</t>
+          <t>-220.4%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-180.5%</t>
+          <t>-170.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.7%</t>
+          <t>-28.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.6%</t>
+          <t>-13.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-144.4%</t>
+          <t>-169.1%</t>
         </is>
       </c>
     </row>
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213499</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.757330812233671</v>
+        <v>-1.587793653476741</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.427054107279866</v>
+        <v>2.494868970782638</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.2862001379165331</v>
+        <v>0.4557372966734629</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.302062939237002</v>
+        <v>3.40378523449116</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416049</v>
+        <v>3.231167537416048</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.7539940657247</v>
+        <v>-1.58445690696777</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.436487556292023</v>
+        <v>2.504302419794795</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.2888921703355645</v>
+        <v>0.4584293290924942</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.311776909096989</v>
+        <v>3.413499204351147</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382332</v>
+        <v>3.235981977382331</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.120705117391245</v>
+        <v>-1.951167958634316</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.290909527669137</v>
+        <v>2.358724391171909</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.07781888133098114</v>
+        <v>0.09171827742594862</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.092856670140794</v>
+        <v>3.194578965394952</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495503</v>
+        <v>3.278199702495502</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.505885508321318</v>
+        <v>-2.336348349564388</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.135379910109971</v>
+        <v>2.203194773612744</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.07781888133098114</v>
+        <v>0.09171827742594862</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.091399208953657</v>
+        <v>3.193121504207815</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.29913614634706</v>
+        <v>3.299136146347058</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.849568281547981</v>
+        <v>-2.680031122791051</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.999675924273922</v>
+        <v>2.067490787776695</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.1857249333581993</v>
+        <v>-0.01618777460126958</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.028424701191943</v>
+        <v>3.130146996446101</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130022</v>
+        <v>3.287377576130021</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.207218631786329</v>
+        <v>-3.037681473029399</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.852721842834841</v>
+        <v>1.920536706337613</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.5433752835965475</v>
+        <v>-0.3738381248396177</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.809940549705192</v>
+        <v>2.911662844959349</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178249</v>
+        <v>3.315884374178248</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.213879572008477</v>
+        <v>-3.044342413251547</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.851830393446241</v>
+        <v>1.919645256949013</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.5433752835965475</v>
+        <v>-0.3738381248396177</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.811713476405451</v>
+        <v>2.913435771659609</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.645685365158264</v>
+        <v>-3.476148206401334</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.665440963653731</v>
+        <v>1.733255827156503</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.6797927800378145</v>
+        <v>-0.5102556212808846</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.716195866008095</v>
+        <v>2.817918161262253</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310987</v>
+        <v>3.284619513310986</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.972117894026008</v>
+        <v>-3.802580735269078</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.523152727108724</v>
+        <v>1.590967590611496</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.7622610305449626</v>
+        <v>-0.5927238717880328</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.654999690705897</v>
+        <v>2.756721985960055</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006539</v>
+        <v>3.305849539006538</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.973682045136311</v>
+        <v>-3.804144886379381</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.521107658320568</v>
+        <v>1.58892252182334</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.7622610305449626</v>
+        <v>-0.5927238717880328</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.653580282361863</v>
+        <v>2.75530257761602</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309429</v>
+        <v>3.311086391309428</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.337308290036624</v>
+        <v>-4.167771131279694</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.382144720594684</v>
+        <v>1.449959584097456</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.8604826674120885</v>
+        <v>-0.6909455086551586</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.601134860475828</v>
+        <v>2.702857155729986</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.30471571697091</v>
+        <v>3.304715716970909</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.334881225507906</v>
+        <v>-4.165344066750976</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.382370061412003</v>
+        <v>1.450184924914775</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.8608154492192401</v>
+        <v>-0.6912782904623102</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.600189706397369</v>
+        <v>2.701912001651527</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330527</v>
+        <v>3.300815818330526</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.743470002688584</v>
+        <v>-4.573932843931654</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.217696094554491</v>
+        <v>1.285510958057263</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.269404226399919</v>
+        <v>-1.099867067642989</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.353797984103721</v>
+        <v>2.455520279357879</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191742</v>
+        <v>3.302618194191741</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.156452486829678</v>
+        <v>-4.986915328072748</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.047688533369514</v>
+        <v>1.115503396872286</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.269404226399919</v>
+        <v>-1.099867067642989</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.348983416575182</v>
+        <v>2.45070571182934</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108644</v>
+        <v>3.305023265108643</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.572844361116675</v>
+        <v>-5.403307202359746</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.8791258342635921</v>
+        <v>0.9469406977663639</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.269404226399919</v>
+        <v>-1.099867067642989</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.346977467184059</v>
+        <v>2.448699762438217</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097825</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.94952137164652</v>
+        <v>-5.77998421288959</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.7387137207203334</v>
+        <v>0.8065285842231051</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.269404226399919</v>
+        <v>-1.099867067642989</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.357236157852738</v>
+        <v>2.458958453106896</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094121</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.963236235971631</v>
+        <v>-5.793699077214701</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.7293273401359843</v>
+        <v>0.7971422036387561</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.269404226399919</v>
+        <v>-1.099867067642989</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.353335722998433</v>
+        <v>2.455058018252591</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119929</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.27606103521661</v>
+        <v>-6.106523876459681</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.6026023404929934</v>
+        <v>0.6704172039957652</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.269404226399919</v>
+        <v>-1.099867067642989</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.351740643053434</v>
+        <v>2.453462938307592</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969599</v>
+        <v>3.424633354969598</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.280874073681948</v>
+        <v>-6.111336914925018</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.6044561010360665</v>
+        <v>0.6722709645388383</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.270950861102704</v>
+        <v>-1.101413702345774</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.354591638160971</v>
+        <v>2.456313933415128</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923092</v>
+        <v>3.419979433923091</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.714223181792184</v>
+        <v>-6.544686023035254</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.427090153257569</v>
+        <v>0.4949050167603408</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.270950861102704</v>
+        <v>-1.101413702345774</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.350565333626568</v>
+        <v>2.452287628880725</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297754</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.097224570534815</v>
+        <v>-6.927687411777885</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.2737874964389326</v>
+        <v>0.3416023599417044</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.270950861102704</v>
+        <v>-1.101413702345774</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.350463232304984</v>
+        <v>2.452185527559141</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.472209896706092</v>
+        <v>-7.302672737949162</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.1263648819418517</v>
+        <v>0.1941797454446235</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.645936187273982</v>
+        <v>-1.476399028517052</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.128043552573647</v>
+        <v>2.229765847827805</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.831740219210094</v>
+        <v>-7.662203060453164</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.01209694376169868</v>
+        <v>0.0557179197410731</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.645936187273982</v>
+        <v>-1.476399028517052</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.133393855871697</v>
+        <v>2.235116151125855</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341317</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.158140247875107</v>
+        <v>-7.988603089118177</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1347409352705262</v>
+        <v>-0.06692607176775445</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.972336215938995</v>
+        <v>-1.802799057182065</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.945469858629867</v>
+        <v>2.047192153884025</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776681</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.151664101081547</v>
+        <v>-7.982126942324618</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1291087259313337</v>
+        <v>-0.06129386242856194</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.965860069145435</v>
+        <v>-1.796322910388505</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.952397297327772</v>
+        <v>2.05411959258193</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.147973176125136</v>
+        <v>-7.978436017368206</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1276323559487693</v>
+        <v>-0.0598174924459971</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.965860069145435</v>
+        <v>-1.796322910388505</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.952397297327772</v>
+        <v>2.05411959258193</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611695</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.352231351455</v>
+        <v>-8.182694192698069</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2038224289620727</v>
+        <v>-0.1360075654593</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.093499013759424</v>
+        <v>-1.923961855002494</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.881327127678021</v>
+        <v>1.983049422932178</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.512870377943365</v>
+        <v>-8.343333219186434</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2635954850729827</v>
+        <v>-0.19578062157021</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.208232486761819</v>
+        <v>-2.03869532800489</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.816969598361019</v>
+        <v>1.918691893615177</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910627</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.439400546275916</v>
+        <v>-8.269863387518985</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2188358509125816</v>
+        <v>-0.1510209874098094</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.134762655094371</v>
+        <v>-1.965225496337441</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.87642319885491</v>
+        <v>1.978145494109068</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.614524963662459</v>
+        <v>-8.444987804905528</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2743303971196824</v>
+        <v>-0.2065155336169098</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.309887072480915</v>
+        <v>-2.140349913723985</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.7859037691705</v>
+        <v>1.887626064424658</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.848977057676949</v>
+        <v>-8.679439898920018</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.375330399627074</v>
+        <v>-0.3075155361243018</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.309887072480915</v>
+        <v>-2.140349913723985</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.778684604268904</v>
+        <v>1.880406899523062</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.136780902214188</v>
+        <v>-8.967243743457256</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4971241282159458</v>
+        <v>-0.4293092647131735</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.597690917018153</v>
+        <v>-2.428153758261223</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.599330106772585</v>
+        <v>1.701052402026743</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.366605349378013</v>
+        <v>-9.197068190621081</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5879381172429197</v>
+        <v>-0.520123253740147</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.760338454088314</v>
+        <v>-2.590801295331384</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.502857374369045</v>
+        <v>1.604579669623203</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.598634269114275</v>
+        <v>-9.429097110357343</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6780559565083095</v>
+        <v>-0.6102410930055373</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.822351151276737</v>
+        <v>-2.652813992519807</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.468343484685106</v>
+        <v>1.570065779939264</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.546618755145461</v>
+        <v>-9.37708159638853</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6532594152343836</v>
+        <v>-0.5854445517316109</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.822351151276737</v>
+        <v>-2.652813992519807</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.472333820371507</v>
+        <v>1.574056115625664</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628919</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.688290596869582</v>
+        <v>-9.51875343811265</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.7114033788227734</v>
+        <v>-0.6435885153200007</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.822351151276737</v>
+        <v>-2.652813992519807</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.470858593472765</v>
+        <v>1.572580888726923</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.787197337328857</v>
+        <v>-9.617660178571926</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.7359126648416114</v>
+        <v>-0.6680978013388388</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.921257891736012</v>
+        <v>-2.751720732979082</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.426567959362072</v>
+        <v>1.52829025461623</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.588045230091758</v>
+        <v>-9.418508071334827</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.6693029555934547</v>
+        <v>-0.601488092090682</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.755935365786199</v>
+        <v>-2.586398207029269</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.512710341285277</v>
+        <v>1.614432636539435</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.362200077372346</v>
+        <v>-9.531972028302311</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.5693858214694814</v>
+        <v>-0.6372946018414671</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.714008690199035</v>
+        <v>-2.631940121636569</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.547445419673784</v>
+        <v>1.596686560811263</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.075925265049651</v>
+        <v>-9.245697215979616</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4537367519843443</v>
+        <v>-0.5216455323563305</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.714008690199035</v>
+        <v>-2.631940121636569</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.548584564229843</v>
+        <v>1.597825705367322</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.849129437976318</v>
+        <v>-9.018901388906283</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3603846469929035</v>
+        <v>-0.4282934273648893</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.645894745577491</v>
+        <v>-2.563826177015025</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.592086705164877</v>
+        <v>1.641327846302356</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.565220707047569</v>
+        <v>-8.734992657977534</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2410874503827674</v>
+        <v>-0.3089962307547531</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.645894745577491</v>
+        <v>-2.563826177015025</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.597820409403513</v>
+        <v>1.647061550540993</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.318233456854617</v>
+        <v>-8.488005407784582</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.1520298126994519</v>
+        <v>-0.2199385930714377</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.398907495384539</v>
+        <v>-2.316838926822073</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.736275497125419</v>
+        <v>1.785516638262899</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.054396589650548</v>
+        <v>-8.224168540580512</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.05637854713073143</v>
+        <v>-0.1242873275027176</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.398907495384539</v>
+        <v>-2.316838926822073</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.726392015812512</v>
+        <v>1.775633156949991</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-7.787154788782151</v>
+        <v>-7.956926739712116</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.04868361271725341</v>
+        <v>-0.01922516765473237</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.398907495384539</v>
+        <v>-2.316838926822073</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.724557455313138</v>
+        <v>1.773798596450618</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-7.511345625381667</v>
+        <v>-7.681117576311632</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.1587069631039864</v>
+        <v>0.09079818273200013</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.309888187105805</v>
+        <v>-2.227819618543339</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.777668725306917</v>
+        <v>1.826909866444397</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-7.242278037614687</v>
+        <v>-7.412049988544652</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.2670025043562716</v>
+        <v>0.1990937239842858</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.040820599338826</v>
+        <v>-1.95875203077636</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.939777784112598</v>
+        <v>1.989018925250078</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-6.978218099291891</v>
+        <v>-7.147990050221856</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.3593661635236378</v>
+        <v>0.291457383151652</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.77676066101603</v>
+        <v>-1.694692092453564</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.084953430944524</v>
+        <v>2.134194572082004</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-6.271138475787053</v>
+        <v>-6.440910426717018</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.6394109792652722</v>
+        <v>0.5715021988932865</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.77676066101603</v>
+        <v>-1.694692092453564</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.082166397284223</v>
+        <v>2.131407538421703</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-6.021497445801101</v>
+        <v>-6.191269396731066</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.7396110151474944</v>
+        <v>0.6717022347755086</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.527119631030078</v>
+        <v>-1.445051062467612</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.232294639163636</v>
+        <v>2.281535780301115</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-5.766955546460025</v>
+        <v>-5.93672749738999</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.8407945961046819</v>
+        <v>0.7728858157326961</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.272577731689003</v>
+        <v>-1.190509163126537</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.384386599989038</v>
+        <v>2.433627741126517</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-5.533474324230427</v>
+        <v>-5.703246275160391</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.9421115138343739</v>
+        <v>0.8742027334623876</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.039096509459404</v>
+        <v>-0.9570279408969382</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.532399762164649</v>
+        <v>2.581640903302129</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-5.353765794086554</v>
+        <v>-5.523537745016519</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.011102715578964</v>
+        <v>0.9431939352069776</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.9819250052967081</v>
+        <v>-0.8998564367342421</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.563810454349308</v>
+        <v>2.613051595486787</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-5.221490320455668</v>
+        <v>-5.391262271385632</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.059380391778345</v>
+        <v>0.9914716114063591</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.8496495316658215</v>
+        <v>-0.7675809631033554</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.638543225274867</v>
+        <v>2.687784366412346</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-5.030890645782515</v>
+        <v>-5.20066259671248</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.138435322335243</v>
+        <v>1.070526541963257</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.6590498569926686</v>
+        <v>-0.5769812884302026</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.755718090766395</v>
+        <v>2.804959231903875</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-4.781890847098934</v>
+        <v>-4.951662798028899</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.250941583032334</v>
+        <v>1.183032802660348</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.6590498569926686</v>
+        <v>-0.5769812884302026</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.768624431990054</v>
+        <v>2.817865573127534</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-4.887480836872038</v>
+        <v>-5.057252787802003</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.080729657523874</v>
+        <v>1.012820877151888</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.7646398467657729</v>
+        <v>-0.6825712782033069</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.577294508526973</v>
+        <v>2.626535649664453</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-4.906215738990635</v>
+        <v>-5.0759876899206</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.121780038553521</v>
+        <v>1.053871258181535</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.7646398467657729</v>
+        <v>-0.6825712782033069</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.625838850404059</v>
+        <v>2.675079991541539</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-4.629477564319822</v>
+        <v>-4.799249515249787</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.235854320407841</v>
+        <v>1.167945540035855</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5828231856558471</v>
+        <v>-0.5007546170933811</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.738307859056009</v>
+        <v>2.787549000193489</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-4.502585157884752</v>
+        <v>-4.672357108814717</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.277897296728391</v>
+        <v>1.209988516356405</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.4559307792207772</v>
+        <v>-0.3738622106583112</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.805729316663573</v>
+        <v>2.854970457801053</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-4.314997649974826</v>
+        <v>-4.484769600904791</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.345971687797268</v>
+        <v>1.278062907425282</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.4559307792207772</v>
+        <v>-0.3738622106583112</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.79876870456848</v>
+        <v>2.84800984570596</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-4.072849256520968</v>
+        <v>-4.242621207450933</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.457293399559955</v>
+        <v>1.389384619187969</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.4559307792207772</v>
+        <v>-0.3738622106583112</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.813231058949623</v>
+        <v>2.862472200087103</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-4.009619884752619</v>
+        <v>-4.179391835682584</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.477117268726489</v>
+        <v>1.409208488354503</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.4559307792207772</v>
+        <v>-0.3738622106583112</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.807763179408818</v>
+        <v>2.857004320546298</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-3.823132192375613</v>
+        <v>-3.992904143305578</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.549210439687868</v>
+        <v>1.481301659315882</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.2694430868437709</v>
+        <v>-0.1873745182813049</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.917153888845599</v>
+        <v>2.966395029983078</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-3.80198299347217</v>
+        <v>-3.971754944402135</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.565371097486571</v>
+        <v>1.497462317114585</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.2482938879403276</v>
+        <v>-0.1662253193778616</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.93754438642499</v>
+        <v>2.98678552756247</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-3.558217551488726</v>
+        <v>-3.727989502418691</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.658657982627</v>
+        <v>1.590749202255014</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.2482938879403276</v>
+        <v>-0.1662253193778616</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.933325094772041</v>
+        <v>2.982566235909521</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-3.294189484295466</v>
+        <v>-3.463961435225431</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.76639352342432</v>
+        <v>1.698484743052334</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.04642848912437403</v>
+        <v>0.035640079438092</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.056568647981629</v>
+        <v>3.105809789119109</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-3.044339090346391</v>
+        <v>-3.214111041276356</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.859075755987652</v>
+        <v>1.791166975615666</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.04642848912437403</v>
+        <v>0.035640079438092</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.049310722965331</v>
+        <v>3.098551864102811</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-2.740771601342413</v>
+        <v>-2.910543552272378</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.984101875109892</v>
+        <v>1.916193094737906</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.04642848912437403</v>
+        <v>0.035640079438092</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.05290984648598</v>
+        <v>3.102150987623459</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.701979533878345</v>
+        <v>3.401172073801201</v>
       </c>
       <c r="C1921" t="n">
-        <v>3.022725832109491</v>
+        <v>2.775818935088742</v>
       </c>
       <c r="D1921" t="n">
-        <v>-2.740771601342413</v>
+        <v>-2.910543552272378</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.984101875109892</v>
+        <v>1.916193094737906</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.04642848912437403</v>
+        <v>0.035640079438092</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.015789629095859</v>
+        <v>2.76888273207511</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240401.xlsx
+++ b/tame_output/ON/bt/strategyON_20240401.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.3%</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-70.7%</t>
+          <t>-74.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.4%</t>
+          <t>110.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.8%</t>
+          <t>127.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-561.6%</t>
+          <t>-588.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.9%</t>
+          <t>-48.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.3%</t>
+          <t>-70.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>494.5%</t>
+          <t>494.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-452.6%</t>
+          <t>-499.3%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-219.2%</t>
+          <t>-235.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-36.5%</t>
+          <t>-37.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-85.1%</t>
+          <t>-114.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-184.6%</t>
+          <t>-203.3%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.8%</t>
+          <t>-24.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-283.3%</t>
+          <t>-292.6%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.3%</t>
+          <t>-32.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-18.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.9%</t>
+          <t>-158.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-220.4%</t>
+          <t>-229.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-170.4%</t>
+          <t>-175.9%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-13.5%</t>
+          <t>-13.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213499</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416048</v>
+        <v>3.231167537416049</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.58445690696777</v>
+        <v>-2.05090301892024</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.504302419794795</v>
+        <v>2.317723975013807</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.4584293290924942</v>
+        <v>0.3652052759943295</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.413499204351147</v>
+        <v>3.357564772492248</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382331</v>
+        <v>3.235981977382332</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-1.951167958634316</v>
+        <v>-2.417614070586785</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.358724391171909</v>
+        <v>2.172145946390921</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.09171827742594862</v>
+        <v>-0.001505775672216103</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.194578965394952</v>
+        <v>3.138644533536053</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495502</v>
+        <v>3.278199702495503</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.336348349564388</v>
+        <v>-2.802794461516858</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.203194773612744</v>
+        <v>2.016616328831756</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.09171827742594862</v>
+        <v>-0.001505775672216103</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.193121504207815</v>
+        <v>3.137187072348917</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347058</v>
+        <v>3.29913614634706</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.680031122791051</v>
+        <v>-3.14647723474352</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.067490787776695</v>
+        <v>1.880912342995707</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.01618777460126958</v>
+        <v>-0.1094118276994343</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.130146996446101</v>
+        <v>3.074212564587202</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130021</v>
+        <v>3.287377576130022</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.037681473029399</v>
+        <v>-3.504127584981868</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.920536706337613</v>
+        <v>1.733958261556625</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.3738381248396177</v>
+        <v>-0.4670621779377824</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.911662844959349</v>
+        <v>2.855728413100451</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178248</v>
+        <v>3.315884374178249</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.044342413251547</v>
+        <v>-3.510788525204016</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.919645256949013</v>
+        <v>1.733066812168025</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.3738381248396177</v>
+        <v>-0.4670621779377824</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.913435771659609</v>
+        <v>2.85750133980071</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.476148206401334</v>
+        <v>-3.942594318353804</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.733255827156503</v>
+        <v>1.546677382375515</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.5102556212808846</v>
+        <v>-0.6034796743790494</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.817918161262253</v>
+        <v>2.761983729403354</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310986</v>
+        <v>3.284619513310987</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.802580735269078</v>
+        <v>-4.269026847221548</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.590967590611496</v>
+        <v>1.404389145830508</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.5927238717880328</v>
+        <v>-0.6859479248861975</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.756721985960055</v>
+        <v>2.700787554101156</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006538</v>
+        <v>3.305849539006539</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.804144886379381</v>
+        <v>-4.270590998331851</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.58892252182334</v>
+        <v>1.402344077042352</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.5927238717880328</v>
+        <v>-0.6859479248861975</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.75530257761602</v>
+        <v>2.699368145757121</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309428</v>
+        <v>3.311086391309429</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.167771131279694</v>
+        <v>-4.634217243232165</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.449959584097456</v>
+        <v>1.263381139316468</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.6909455086551586</v>
+        <v>-0.7841695617533233</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.702857155729986</v>
+        <v>2.646922723871088</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970909</v>
+        <v>3.30471571697091</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.165344066750976</v>
+        <v>-4.631790178703446</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.450184924914775</v>
+        <v>1.263606480133787</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.6912782904623102</v>
+        <v>-0.784502343560475</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.701912001651527</v>
+        <v>2.645977569792628</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330526</v>
+        <v>3.300815818330527</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.573932843931654</v>
+        <v>-5.040378955884124</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.285510958057263</v>
+        <v>1.098932513276275</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.099867067642989</v>
+        <v>-1.193091120741153</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.455520279357879</v>
+        <v>2.39958584749898</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191741</v>
+        <v>3.302618194191742</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-4.986915328072748</v>
+        <v>-5.453361440025218</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.115503396872286</v>
+        <v>0.9289249520912977</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.099867067642989</v>
+        <v>-1.193091120741153</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.45070571182934</v>
+        <v>2.394771279970441</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108643</v>
+        <v>3.305023265108644</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.403307202359746</v>
+        <v>-5.869753314312216</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.9469406977663639</v>
+        <v>0.760362252985376</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.099867067642989</v>
+        <v>-1.193091120741153</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.448699762438217</v>
+        <v>2.392765330579318</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097825</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.77998421288959</v>
+        <v>-6.24643032484206</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.8065285842231051</v>
+        <v>0.6199501394421172</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.099867067642989</v>
+        <v>-1.193091120741153</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.458958453106896</v>
+        <v>2.403024021247997</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094121</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.793699077214701</v>
+        <v>-6.260145189167171</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.7971422036387561</v>
+        <v>0.6105637588577681</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.099867067642989</v>
+        <v>-1.193091120741153</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.455058018252591</v>
+        <v>2.399123586393692</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.40596051119929</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.106523876459681</v>
+        <v>-6.572969988412151</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.6704172039957652</v>
+        <v>0.4838387592147773</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.099867067642989</v>
+        <v>-1.193091120741153</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.453462938307592</v>
+        <v>2.397528506448693</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969599</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.111336914925018</v>
+        <v>-6.577783026877488</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.6722709645388383</v>
+        <v>0.4856925197578503</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.101413702345774</v>
+        <v>-1.194637755443939</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.456313933415128</v>
+        <v>2.40037950155623</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.419979433923092</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.544686023035254</v>
+        <v>-7.011132134987724</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.4949050167603408</v>
+        <v>0.3083265719793529</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.101413702345774</v>
+        <v>-1.194637755443939</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.452287628880725</v>
+        <v>2.396353197021827</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297754</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-6.927687411777885</v>
+        <v>-7.394133523730355</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.3416023599417044</v>
+        <v>0.1550239151607165</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.101413702345774</v>
+        <v>-1.194637755443939</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.452185527559141</v>
+        <v>2.396251095700243</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.302672737949162</v>
+        <v>-7.769118849901632</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.1941797454446235</v>
+        <v>0.007601300663635513</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.476399028517052</v>
+        <v>-1.569623081615217</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.229765847827805</v>
+        <v>2.173831415968906</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.662203060453164</v>
+        <v>-8.128649172405634</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.0557179197410731</v>
+        <v>-0.1308605250399149</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.476399028517052</v>
+        <v>-1.569623081615217</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.235116151125855</v>
+        <v>2.179181719266956</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341317</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.988603089118177</v>
+        <v>-8.455049201070647</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.06692607176775445</v>
+        <v>-0.2535045165487424</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.802799057182065</v>
+        <v>-1.896023110280229</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.047192153884025</v>
+        <v>1.991257722025126</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776681</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-7.982126942324618</v>
+        <v>-8.448573054277087</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.06129386242856194</v>
+        <v>-0.2478723072095499</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.796322910388505</v>
+        <v>-1.88954696348667</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.05411959258193</v>
+        <v>1.998185160723031</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407492</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-7.978436017368206</v>
+        <v>-8.444882129320677</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.0598174924459971</v>
+        <v>-0.2463959372269855</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.796322910388505</v>
+        <v>-1.88954696348667</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.05411959258193</v>
+        <v>1.998185160723031</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611695</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.182694192698069</v>
+        <v>-8.64914030465054</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1360075654593</v>
+        <v>-0.3225860102402889</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.923961855002494</v>
+        <v>-2.017185908100659</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.983049422932178</v>
+        <v>1.92711499107328</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.343333219186434</v>
+        <v>-8.809779331138905</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.19578062157021</v>
+        <v>-0.3823590663511989</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.03869532800489</v>
+        <v>-2.131919381103054</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.918691893615177</v>
+        <v>1.862757461756279</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910627</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.269863387518985</v>
+        <v>-8.736309499471457</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1510209874098094</v>
+        <v>-0.3375994321907978</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.965225496337441</v>
+        <v>-2.058449549435606</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.978145494109068</v>
+        <v>1.922211062250168</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.444987804905528</v>
+        <v>-8.911433916858</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2065155336169098</v>
+        <v>-0.3930939783978986</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.140349913723985</v>
+        <v>-2.23357396682215</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.887626064424658</v>
+        <v>1.831691632565759</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.679439898920018</v>
+        <v>-9.14588601087249</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3075155361243018</v>
+        <v>-0.4940939809052902</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.140349913723985</v>
+        <v>-2.23357396682215</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.880406899523062</v>
+        <v>1.824472467664163</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.967243743457256</v>
+        <v>-9.433689855409728</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4293092647131735</v>
+        <v>-0.6158877094941619</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.428153758261223</v>
+        <v>-2.521377811359388</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.701052402026743</v>
+        <v>1.645117970167844</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.197068190621081</v>
+        <v>-9.663514302573553</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.520123253740147</v>
+        <v>-0.7067016985211358</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.590801295331384</v>
+        <v>-2.684025348429548</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.604579669623203</v>
+        <v>1.548645237764304</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.429097110357343</v>
+        <v>-9.895543222309815</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6102410930055373</v>
+        <v>-0.7968195377865257</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.652813992519807</v>
+        <v>-2.746038045617972</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.570065779939264</v>
+        <v>1.514131348080365</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.37708159638853</v>
+        <v>-9.843527708341002</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5854445517316109</v>
+        <v>-0.7720229965125998</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.652813992519807</v>
+        <v>-2.746038045617972</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.574056115625664</v>
+        <v>1.518121683766766</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.51875343811265</v>
+        <v>-9.985199550065122</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6435885153200007</v>
+        <v>-0.8301669601009896</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.652813992519807</v>
+        <v>-2.746038045617972</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.572580888726923</v>
+        <v>1.516646456868024</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.617660178571926</v>
+        <v>-10.0841062905244</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6680978013388388</v>
+        <v>-0.8546762461198276</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.751720732979082</v>
+        <v>-2.844944786077247</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.52829025461623</v>
+        <v>1.472355822757331</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.418508071334827</v>
+        <v>-9.884954183287299</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.601488092090682</v>
+        <v>-0.7880665368716708</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.586398207029269</v>
+        <v>-2.679622260127434</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.614432636539435</v>
+        <v>1.558498204680536</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.531972028302311</v>
+        <v>-9.998418140254783</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.6372946018414671</v>
+        <v>-0.823873046622456</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.631940121636569</v>
+        <v>-2.725164174734735</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.596686560811263</v>
+        <v>1.540752128952364</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.245697215979616</v>
+        <v>-9.712143327932088</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.5216455323563305</v>
+        <v>-0.7082239771373189</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.631940121636569</v>
+        <v>-2.725164174734735</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.597825705367322</v>
+        <v>1.541891273508423</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.018901388906283</v>
+        <v>-9.485347500858754</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4282934273648893</v>
+        <v>-0.6148718721458781</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.563826177015025</v>
+        <v>-2.65705023011319</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.641327846302356</v>
+        <v>1.585393414443457</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.734992657977534</v>
+        <v>-9.201438769930006</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3089962307547531</v>
+        <v>-0.495574675535742</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.563826177015025</v>
+        <v>-2.65705023011319</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.647061550540993</v>
+        <v>1.591127118682094</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.488005407784582</v>
+        <v>-8.954451519737054</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2199385930714377</v>
+        <v>-0.4065170378524265</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.316838926822073</v>
+        <v>-2.410062979920238</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.785516638262899</v>
+        <v>1.729582206404</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.224168540580512</v>
+        <v>-8.690614652532984</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.1242873275027176</v>
+        <v>-0.310865772283706</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.316838926822073</v>
+        <v>-2.410062979920238</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.775633156949991</v>
+        <v>1.719698725091092</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-7.956926739712116</v>
+        <v>-8.423372851664586</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.01922516765473237</v>
+        <v>-0.2058036124357208</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.316838926822073</v>
+        <v>-2.410062979920238</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.773798596450618</v>
+        <v>1.717864164591719</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-7.681117576311632</v>
+        <v>-8.147563688264102</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.09079818273200013</v>
+        <v>-0.09578026204898782</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.227819618543339</v>
+        <v>-2.321043671641505</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.826909866444397</v>
+        <v>1.770975434585498</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-7.412049988544652</v>
+        <v>-7.878496100497122</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.1990937239842858</v>
+        <v>0.01251527920329787</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.95875203077636</v>
+        <v>-2.051976083874525</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.989018925250078</v>
+        <v>1.933084493391179</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-7.147990050221856</v>
+        <v>-7.614436162174326</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.291457383151652</v>
+        <v>0.1048789383706641</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.694692092453564</v>
+        <v>-1.787916145551729</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.134194572082004</v>
+        <v>2.078260140223104</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-6.440910426717018</v>
+        <v>-6.907356538669488</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.5715021988932865</v>
+        <v>0.3849237541122985</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.694692092453564</v>
+        <v>-1.787916145551729</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.131407538421703</v>
+        <v>2.075473106562804</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-6.191269396731066</v>
+        <v>-6.657715508683536</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.6717022347755086</v>
+        <v>0.4851237899945207</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.445051062467612</v>
+        <v>-1.538275115565777</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.281535780301115</v>
+        <v>2.225601348442216</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-5.93672749738999</v>
+        <v>-6.40317360934246</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.7728858157326961</v>
+        <v>0.5863073709517082</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.190509163126537</v>
+        <v>-1.283733216224702</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.433627741126517</v>
+        <v>2.377693309267618</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-5.703246275160391</v>
+        <v>-6.169692387112861</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.8742027334623876</v>
+        <v>0.6876242886813997</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.9570279408969382</v>
+        <v>-1.050251993995103</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.581640903302129</v>
+        <v>2.52570647144323</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-5.523537745016519</v>
+        <v>-5.989983856968989</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.9431939352069776</v>
+        <v>0.7566154904259896</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.8998564367342421</v>
+        <v>-0.9930804898324073</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.613051595486787</v>
+        <v>2.557117163627888</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-5.391262271385632</v>
+        <v>-5.857708383338102</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.9914716114063591</v>
+        <v>0.8048931666253711</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.7675809631033554</v>
+        <v>-0.8608050162015206</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.687784366412346</v>
+        <v>2.631849934553447</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-5.20066259671248</v>
+        <v>-5.66710870866495</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.070526541963257</v>
+        <v>0.8839480971822691</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.5769812884302026</v>
+        <v>-0.6702053415283677</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.804959231903875</v>
+        <v>2.749024800044976</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-4.951662798028899</v>
+        <v>-5.418108909981369</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.183032802660348</v>
+        <v>0.9964543578793603</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.5769812884302026</v>
+        <v>-0.6702053415283677</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.817865573127534</v>
+        <v>2.761931141268635</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-5.057252787802003</v>
+        <v>-5.523698899754473</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.012820877151888</v>
+        <v>0.8262424323708997</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6825712782033069</v>
+        <v>-0.775795331301472</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.626535649664453</v>
+        <v>2.570601217805554</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-5.0759876899206</v>
+        <v>-5.54243380187307</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.053871258181535</v>
+        <v>0.8672928134005473</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6825712782033069</v>
+        <v>-0.775795331301472</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.675079991541539</v>
+        <v>2.61914555968264</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-4.799249515249787</v>
+        <v>-5.265695627202257</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.167945540035855</v>
+        <v>0.9813670952548672</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5007546170933811</v>
+        <v>-0.5939786701915463</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.787549000193489</v>
+        <v>2.73161456833459</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-4.672357108814717</v>
+        <v>-5.138803220767187</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.209988516356405</v>
+        <v>1.023410071575417</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.3738622106583112</v>
+        <v>-0.4670862637564763</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.854970457801053</v>
+        <v>2.799036025942153</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-4.484769600904791</v>
+        <v>-4.951215712857261</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.278062907425282</v>
+        <v>1.091484462644294</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.3738622106583112</v>
+        <v>-0.4670862637564763</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.84800984570596</v>
+        <v>2.79207541384706</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-4.242621207450933</v>
+        <v>-4.709067319403403</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.389384619187969</v>
+        <v>1.202806174406981</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.3738622106583112</v>
+        <v>-0.4670862637564763</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.862472200087103</v>
+        <v>2.806537768228203</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-4.179391835682584</v>
+        <v>-4.645837947635054</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.409208488354503</v>
+        <v>1.222630043573515</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.3738622106583112</v>
+        <v>-0.4670862637564763</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.857004320546298</v>
+        <v>2.801069888687398</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-3.992904143305578</v>
+        <v>-4.459350255258048</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.481301659315882</v>
+        <v>1.294723214534894</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1873745182813049</v>
+        <v>-0.2805985713794701</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.966395029983078</v>
+        <v>2.910460598124179</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-3.971754944402135</v>
+        <v>-4.438201056354605</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.497462317114585</v>
+        <v>1.310883872333597</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.1662253193778616</v>
+        <v>-0.2594493724760267</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.98678552756247</v>
+        <v>2.930851095703571</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-3.727989502418691</v>
+        <v>-4.194435614371161</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.590749202255014</v>
+        <v>1.404170757474026</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.1662253193778616</v>
+        <v>-0.2594493724760267</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.982566235909521</v>
+        <v>2.926631804050622</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-3.463961435225431</v>
+        <v>-3.930407547177901</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.698484743052334</v>
+        <v>1.511906298271346</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.035640079438092</v>
+        <v>-0.05758397366007317</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.105809789119109</v>
+        <v>3.04987535726021</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-3.214111041276356</v>
+        <v>-3.680557153228826</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.791166975615666</v>
+        <v>1.604588530834678</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.035640079438092</v>
+        <v>-0.05758397366007317</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.098551864102811</v>
+        <v>3.042617432243912</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-2.910543552272378</v>
+        <v>-3.376989664224848</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.916193094737906</v>
+        <v>1.729614649956918</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.035640079438092</v>
+        <v>-0.05758397366007317</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.102150987623459</v>
+        <v>3.04621655576456</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.401172073801201</v>
+        <v>3.403825498936717</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.775818935088742</v>
+        <v>2.775937386948818</v>
       </c>
       <c r="D1921" t="n">
-        <v>-2.910543552272378</v>
+        <v>-3.376989664224848</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.916193094737906</v>
+        <v>1.729614649956918</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.035640079438092</v>
+        <v>-0.05758397366007317</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.76888273207511</v>
+        <v>2.769001183935186</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240401.xlsx
+++ b/tame_output/ON/bt/strategyON_20240401.xlsx
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,75 +801,75 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-30.5%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-34.0%</t>
+          <t>-2.2%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.0%</t>
+          <t>-71.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.2%</t>
+          <t>111.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.1%</t>
+          <t>127.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>94.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-588.5%</t>
+          <t>-591.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.7%</t>
+          <t>-48.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,32 +1007,32 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.0%</t>
+          <t>-65.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>494.3%</t>
+          <t>495.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-499.3%</t>
+          <t>-439.4%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-235.8%</t>
+          <t>-237.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.9%</t>
+          <t>-38.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-114.9%</t>
+          <t>-71.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-203.3%</t>
+          <t>-178.0%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-292.6%</t>
+          <t>-294.0%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,47 +1308,47 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.9%</t>
+          <t>-33.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.3%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>-172.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-158.2%</t>
+          <t>-160.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-229.8%</t>
+          <t>-193.5%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1451,62 +1451,62 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-175.9%</t>
+          <t>-176.8%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.3%</t>
+          <t>-28.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-13.7%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-169.1%</t>
+          <t>-118.3%</t>
         </is>
       </c>
     </row>
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.05090301892024</v>
+        <v>-2.081118525011919</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.317723975013807</v>
+        <v>2.305637772577136</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3652052759943295</v>
+        <v>0.3507511824338441</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.357564772492248</v>
+        <v>3.348892316355957</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.417614070586785</v>
+        <v>-2.447829576678465</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.172145946390921</v>
+        <v>2.160059743954249</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.001505775672216103</v>
+        <v>-0.01595986923270148</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.138644533536053</v>
+        <v>3.129972077399762</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.802794461516858</v>
+        <v>-2.833009967608537</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.016616328831756</v>
+        <v>2.004530126395084</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.001505775672216103</v>
+        <v>-0.01595986923270148</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.137187072348917</v>
+        <v>3.128514616212625</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.14647723474352</v>
+        <v>-3.1766927408352</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.880912342995707</v>
+        <v>1.868826140559035</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.1094118276994343</v>
+        <v>-0.1238659212599197</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.074212564587202</v>
+        <v>3.06554010845091</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.504127584981868</v>
+        <v>-3.534343091073548</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.733958261556625</v>
+        <v>1.721872059119953</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.4670621779377824</v>
+        <v>-0.4815162714982678</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.855728413100451</v>
+        <v>2.84705595696416</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.510788525204016</v>
+        <v>-3.541004031295696</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.733066812168025</v>
+        <v>1.720980609731354</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.4670621779377824</v>
+        <v>-0.4815162714982678</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.85750133980071</v>
+        <v>2.848828883664419</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.942594318353804</v>
+        <v>-3.972809824445484</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.546677382375515</v>
+        <v>1.534591179938843</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.6034796743790494</v>
+        <v>-0.6179337679395348</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.761983729403354</v>
+        <v>2.753311273267063</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.269026847221548</v>
+        <v>-4.299242353313227</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.404389145830508</v>
+        <v>1.392302943393836</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.6859479248861975</v>
+        <v>-0.700402018446683</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.700787554101156</v>
+        <v>2.692115097964865</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.270590998331851</v>
+        <v>-4.30080650442353</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.402344077042352</v>
+        <v>1.39025787460568</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.6859479248861975</v>
+        <v>-0.700402018446683</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.699368145757121</v>
+        <v>2.69069568962083</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.634217243232165</v>
+        <v>-4.664432749323844</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.263381139316468</v>
+        <v>1.251294936879796</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.7841695617533233</v>
+        <v>-0.7986236553138089</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.646922723871088</v>
+        <v>2.638250267734796</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.631790178703446</v>
+        <v>-4.662005684795125</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.263606480133787</v>
+        <v>1.251520277697115</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.784502343560475</v>
+        <v>-0.7989564371209605</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.645977569792628</v>
+        <v>2.637305113656336</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.040378955884124</v>
+        <v>-5.070594461975804</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.098932513276275</v>
+        <v>1.086846310839602</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.193091120741153</v>
+        <v>-1.207545214301639</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.39958584749898</v>
+        <v>2.390913391362688</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.453361440025218</v>
+        <v>-5.483576946116898</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.9289249520912977</v>
+        <v>0.9168387496546253</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.193091120741153</v>
+        <v>-1.207545214301639</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.394771279970441</v>
+        <v>2.386098823834149</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.869753314312216</v>
+        <v>-5.899968820403895</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.760362252985376</v>
+        <v>0.7482760505487041</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.193091120741153</v>
+        <v>-1.207545214301639</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.392765330579318</v>
+        <v>2.384092874443026</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.24643032484206</v>
+        <v>-6.27664583093374</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.6199501394421172</v>
+        <v>0.6078639370054448</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.193091120741153</v>
+        <v>-1.207545214301639</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.403024021247997</v>
+        <v>2.394351565111705</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.260145189167171</v>
+        <v>-6.290360695258851</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.6105637588577681</v>
+        <v>0.5984775564210958</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.193091120741153</v>
+        <v>-1.207545214301639</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.399123586393692</v>
+        <v>2.390451130257401</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.572969988412151</v>
+        <v>-6.603185494503831</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.4838387592147773</v>
+        <v>0.4717525567781049</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.193091120741153</v>
+        <v>-1.207545214301639</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.397528506448693</v>
+        <v>2.388856050312402</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.577783026877488</v>
+        <v>-6.607998532969168</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.4856925197578503</v>
+        <v>0.473606317321178</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.194637755443939</v>
+        <v>-1.209091849004425</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.40037950155623</v>
+        <v>2.391707045419938</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.011132134987724</v>
+        <v>-7.041347641079404</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.3083265719793529</v>
+        <v>0.2962403695426805</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.194637755443939</v>
+        <v>-1.209091849004425</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.396353197021827</v>
+        <v>2.387680740885535</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.394133523730355</v>
+        <v>-7.424349029822035</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.1550239151607165</v>
+        <v>0.1429377127240441</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.194637755443939</v>
+        <v>-1.209091849004425</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.396251095700243</v>
+        <v>2.387578639563951</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.769118849901632</v>
+        <v>-7.799334355993312</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.007601300663635513</v>
+        <v>-0.004484901773036842</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.569623081615217</v>
+        <v>-1.584077175175702</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.173831415968906</v>
+        <v>2.165158959832615</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.128649172405634</v>
+        <v>-8.158864678497313</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1308605250399149</v>
+        <v>-0.1429467274765872</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.569623081615217</v>
+        <v>-1.584077175175702</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.179181719266956</v>
+        <v>2.170509263130665</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.455049201070647</v>
+        <v>-8.485264707162326</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.2535045165487424</v>
+        <v>-0.2655907189854148</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.896023110280229</v>
+        <v>-1.910477203840715</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.991257722025126</v>
+        <v>1.982585265888835</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.448573054277087</v>
+        <v>-8.478788560368766</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2478723072095499</v>
+        <v>-0.2599585096462222</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.88954696348667</v>
+        <v>-1.904001057047155</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.998185160723031</v>
+        <v>1.98951270458674</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.444882129320677</v>
+        <v>-8.475097635412356</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.2463959372269855</v>
+        <v>-0.2584821396636579</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.88954696348667</v>
+        <v>-1.904001057047155</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.998185160723031</v>
+        <v>1.98951270458674</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.64914030465054</v>
+        <v>-8.679355810742219</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3225860102402889</v>
+        <v>-0.3346722126769608</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.017185908100659</v>
+        <v>-2.031640001661144</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.92711499107328</v>
+        <v>1.918442534936989</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.809779331138905</v>
+        <v>-8.839994837230584</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3823590663511989</v>
+        <v>-0.3944452687878708</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.131919381103054</v>
+        <v>-2.14637347466354</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.862757461756279</v>
+        <v>1.854085005619987</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.736309499471457</v>
+        <v>-8.766525005563135</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3375994321907978</v>
+        <v>-0.3496856346274702</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.058449549435606</v>
+        <v>-2.072903642996092</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.922211062250168</v>
+        <v>1.913538606113877</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.911433916858</v>
+        <v>-8.941649422949679</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3930939783978986</v>
+        <v>-0.405180180834571</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.23357396682215</v>
+        <v>-2.248028060382635</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.831691632565759</v>
+        <v>1.823019176429468</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.14588601087249</v>
+        <v>-9.176101516964168</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4940939809052902</v>
+        <v>-0.5061801833419626</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.23357396682215</v>
+        <v>-2.248028060382635</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.824472467664163</v>
+        <v>1.815800011527872</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.433689855409728</v>
+        <v>-9.463905361501407</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.6158877094941619</v>
+        <v>-0.6279739119308343</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.521377811359388</v>
+        <v>-2.535831904919874</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.645117970167844</v>
+        <v>1.636445514031553</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.663514302573553</v>
+        <v>-9.693729808665232</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.7067016985211358</v>
+        <v>-0.7187879009578078</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.684025348429548</v>
+        <v>-2.698479441990034</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.548645237764304</v>
+        <v>1.539972781628013</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.895543222309815</v>
+        <v>-9.925758728401494</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.7968195377865257</v>
+        <v>-0.8089057402231981</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.746038045617972</v>
+        <v>-2.760492139178457</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.514131348080365</v>
+        <v>1.505458891944073</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.843527708341002</v>
+        <v>-9.873743214432681</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.7720229965125998</v>
+        <v>-0.7841091989492721</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.746038045617972</v>
+        <v>-2.760492139178457</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.518121683766766</v>
+        <v>1.509449227630474</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.985199550065122</v>
+        <v>-10.0154150561568</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.8301669601009896</v>
+        <v>-0.8422531625376619</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.746038045617972</v>
+        <v>-2.760492139178457</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.516646456868024</v>
+        <v>1.507974000731733</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.0841062905244</v>
+        <v>-10.11432179661608</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.8546762461198276</v>
+        <v>-0.8667624485564995</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.844944786077247</v>
+        <v>-2.859398879637733</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.472355822757331</v>
+        <v>1.46368336662104</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.884954183287299</v>
+        <v>-9.915169689378978</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.7880665368716708</v>
+        <v>-0.8001527393083432</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.679622260127434</v>
+        <v>-2.694076353687919</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.558498204680536</v>
+        <v>1.549825748544245</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.998418140254783</v>
+        <v>-9.689324536659567</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.823873046622456</v>
+        <v>-0.7002356051843703</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.725164174734735</v>
+        <v>-2.652149678100756</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.540752128952364</v>
+        <v>1.584560826932752</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.712143327932088</v>
+        <v>-9.403049724336872</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.7082239771373189</v>
+        <v>-0.5845865356992337</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.725164174734735</v>
+        <v>-2.652149678100756</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.541891273508423</v>
+        <v>1.58569997148881</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.485347500858754</v>
+        <v>-9.176253897263539</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.6148718721458781</v>
+        <v>-0.4912344307077925</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.65705023011319</v>
+        <v>-2.584035733479211</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.585393414443457</v>
+        <v>1.629202112423845</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.201438769930006</v>
+        <v>-8.89234516633479</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.495574675535742</v>
+        <v>-0.3719372340976563</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.65705023011319</v>
+        <v>-2.584035733479211</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.591127118682094</v>
+        <v>1.634935816662481</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.954451519737054</v>
+        <v>-8.645357916141839</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.4065170378524265</v>
+        <v>-0.2828795964143409</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.410062979920238</v>
+        <v>-2.337048483286259</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.729582206404</v>
+        <v>1.773390904384387</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.690614652532984</v>
+        <v>-8.381521048937769</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.310865772283706</v>
+        <v>-0.1872283308456208</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.410062979920238</v>
+        <v>-2.337048483286259</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.719698725091092</v>
+        <v>1.76350742307148</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.423372851664586</v>
+        <v>-8.114279248069371</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2058036124357208</v>
+        <v>-0.08216617099763512</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.410062979920238</v>
+        <v>-2.337048483286259</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.717864164591719</v>
+        <v>1.761672862572106</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.147563688264102</v>
+        <v>-7.838470084668887</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.09578026204898782</v>
+        <v>0.02785717938909738</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.321043671641505</v>
+        <v>-2.248029175007526</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.770975434585498</v>
+        <v>1.814784132565885</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-7.878496100497122</v>
+        <v>-7.569402496901907</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.01251527920329787</v>
+        <v>0.1361527206413831</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.051976083874525</v>
+        <v>-1.978961587240546</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.933084493391179</v>
+        <v>1.976893191371566</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-7.614436162174326</v>
+        <v>-7.305342558579111</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.1048789383706641</v>
+        <v>0.2285163798087493</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.787916145551729</v>
+        <v>-1.71490164891775</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.078260140223104</v>
+        <v>2.122068838203492</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-6.907356538669488</v>
+        <v>-6.598262935074273</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.3849237541122985</v>
+        <v>0.5085611955503837</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.787916145551729</v>
+        <v>-1.71490164891775</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.075473106562804</v>
+        <v>2.119281804543191</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-6.657715508683536</v>
+        <v>-6.348621905088321</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.4851237899945207</v>
+        <v>0.6087612314326059</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.538275115565777</v>
+        <v>-1.465260618931798</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.225601348442216</v>
+        <v>2.269410046422604</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-6.40317360934246</v>
+        <v>-6.094080005747246</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.5863073709517082</v>
+        <v>0.7099448123897929</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.283733216224702</v>
+        <v>-1.210718719590723</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.377693309267618</v>
+        <v>2.421502007248006</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.169692387112861</v>
+        <v>-5.860598783517648</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.6876242886813997</v>
+        <v>0.8112617301194844</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.050251993995103</v>
+        <v>-0.9772374973611244</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.52570647144323</v>
+        <v>2.569515169423617</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-5.989983856968989</v>
+        <v>-5.680890253373775</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.7566154904259896</v>
+        <v>0.8802529318640744</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.9930804898324073</v>
+        <v>-0.9200659931984283</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.557117163627888</v>
+        <v>2.600925861608276</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-5.857708383338102</v>
+        <v>-5.548614779742889</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.8048931666253711</v>
+        <v>0.9285306080634559</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.8608050162015206</v>
+        <v>-0.7877905195675416</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.631849934553447</v>
+        <v>2.675658632533835</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-5.66710870866495</v>
+        <v>-5.358015105069736</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.8839480971822691</v>
+        <v>1.007585538620354</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.6702053415283677</v>
+        <v>-0.5971908448943888</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.749024800044976</v>
+        <v>2.792833498025363</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-5.418108909981369</v>
+        <v>-5.109015306386155</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.9964543578793603</v>
+        <v>1.120091799317445</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.6702053415283677</v>
+        <v>-0.5971908448943888</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.761931141268635</v>
+        <v>2.805739839249022</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-5.523698899754473</v>
+        <v>-5.214605296159259</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.8262424323708997</v>
+        <v>0.9498798738089844</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.775795331301472</v>
+        <v>-0.7027808346674931</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.570601217805554</v>
+        <v>2.614409915785941</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-5.54243380187307</v>
+        <v>-5.233340198277856</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.8672928134005473</v>
+        <v>0.9909302548386321</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.775795331301472</v>
+        <v>-0.7027808346674931</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.61914555968264</v>
+        <v>2.662954257663027</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-5.265695627202257</v>
+        <v>-4.956602023607044</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.9813670952548672</v>
+        <v>1.105004536692952</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5939786701915463</v>
+        <v>-0.5209641735575673</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.73161456833459</v>
+        <v>2.775423266314977</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-5.138803220767187</v>
+        <v>-4.829709617171973</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.023410071575417</v>
+        <v>1.147047513013502</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.4670862637564763</v>
+        <v>-0.3940717671224974</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.799036025942153</v>
+        <v>2.842844723922541</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-4.951215712857261</v>
+        <v>-4.642122109262047</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.091484462644294</v>
+        <v>1.215121904082379</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.4670862637564763</v>
+        <v>-0.3940717671224974</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.79207541384706</v>
+        <v>2.835884111827448</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-4.709067319403403</v>
+        <v>-4.399973715808189</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.202806174406981</v>
+        <v>1.326443615845065</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.4670862637564763</v>
+        <v>-0.3940717671224974</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.806537768228203</v>
+        <v>2.850346466208591</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-4.645837947635054</v>
+        <v>-4.336744344039841</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.222630043573515</v>
+        <v>1.3462674850116</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.4670862637564763</v>
+        <v>-0.3940717671224974</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.801069888687398</v>
+        <v>2.844878586667786</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-4.459350255258048</v>
+        <v>-4.150256651662835</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.294723214534894</v>
+        <v>1.418360655972979</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.2805985713794701</v>
+        <v>-0.2075840747454911</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.910460598124179</v>
+        <v>2.954269296104567</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-4.438201056354605</v>
+        <v>-4.129107452759391</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.310883872333597</v>
+        <v>1.434521313771682</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.2594493724760267</v>
+        <v>-0.1864348758420478</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.930851095703571</v>
+        <v>2.974659793683958</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-4.194435614371161</v>
+        <v>-3.885342010775947</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.404170757474026</v>
+        <v>1.527808198912111</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.2594493724760267</v>
+        <v>-0.1864348758420478</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.926631804050622</v>
+        <v>2.970440502031009</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-3.930407547177901</v>
+        <v>-3.621313943582687</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.511906298271346</v>
+        <v>1.635543739709431</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.05758397366007317</v>
+        <v>0.01543052297390579</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.04987535726021</v>
+        <v>3.093684055240597</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-3.680557153228826</v>
+        <v>-3.371463549633612</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.604588530834678</v>
+        <v>1.728225972272762</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.05758397366007317</v>
+        <v>0.01543052297390579</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.042617432243912</v>
+        <v>3.086426130224299</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-3.376989664224848</v>
+        <v>-3.067896060629634</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.729614649956918</v>
+        <v>1.853252091395003</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.05758397366007317</v>
+        <v>0.01543052297390579</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.04621655576456</v>
+        <v>3.090025253744948</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.403825498936717</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.775937386948818</v>
+        <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-3.376989664224848</v>
+        <v>-2.778235582240658</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.729614649956918</v>
+        <v>1.982443788805146</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.05758397366007317</v>
+        <v>0.3050910013628818</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.769001183935186</v>
+        <v>3.277149046832887</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240401.xlsx
+++ b/tame_output/ON/bt/strategyON_20240401.xlsx
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-172.9%</t>
+          <t>-172.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416049</v>
+        <v>3.231167537416048</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.29913614634706</v>
+        <v>3.299136146347059</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081569</v>
+        <v>3.76894809908157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425329</v>
+        <v>3.72857435442533</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702414</v>
+        <v>3.747699084702415</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906229</v>
+        <v>3.76631350390623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.78468094578195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567246</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487773</v>
+        <v>3.789307536487775</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309729</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858729</v>
+        <v>3.839370871858731</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761806</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430986</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568105</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192815</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788093</v>
+        <v>3.748324832788095</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527524</v>
+        <v>3.824307657527526</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749183</v>
+        <v>3.826351398749185</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481496</v>
+        <v>3.835954411481498</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.403825498936717</v>
+        <v>3.403825498936718</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-2.778235582240658</v>
+        <v>-2.778393983270358</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.982443788805146</v>
+        <v>1.982380428393267</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.3050910013628818</v>
+        <v>0.3049326003331813</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.277149046832887</v>
+        <v>3.277054006215067</v>
       </c>
     </row>
   </sheetData>
